--- a/Source/SmartInventory/SmartInventory/Content/Templates/Site/ImportSite.xlsx
+++ b/Source/SmartInventory/SmartInventory/Content/Templates/Site/ImportSite.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19040" windowHeight="7480"/>
+    <workbookView windowWidth="19035" windowHeight="7620"/>
   </bookViews>
   <sheets>
     <sheet name="Site" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Site ID</t>
   </si>
@@ -35,9 +35,6 @@
     <t>Site Name</t>
   </si>
   <si>
-    <t>Maximum Cost</t>
-  </si>
-  <si>
     <t>Project Category</t>
   </si>
   <si>
@@ -65,13 +62,10 @@
     <t>Fiber Link Code</t>
   </si>
   <si>
-    <t>Site12DEEP5</t>
+    <t>Site2025060902</t>
   </si>
   <si>
     <t>Pamunuwa_South3</t>
-  </si>
-  <si>
-    <t>2.5Mn</t>
   </si>
   <si>
     <t>DM Sprouts RO - Macro</t>
@@ -292,73 +286,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -640,7 +634,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -664,16 +658,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -682,30 +676,30 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -764,7 +758,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -774,20 +768,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1068,6 +1059,13 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
+<customStorage xmlns="https://web.wps.cn/et/2018/main">
+  <book/>
+  <sheets/>
+</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1328,35 +1326,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelRow="3"/>
+  <dimension ref="A1:M4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="10.8" customWidth="1"/>
-    <col min="2" max="3" width="10.2636363636364" customWidth="1"/>
-    <col min="4" max="4" width="34.5272727272727" customWidth="1"/>
-    <col min="5" max="5" width="13.6" customWidth="1"/>
-    <col min="6" max="6" width="24.3636363636364" customWidth="1"/>
-    <col min="7" max="7" width="17.8636363636364" customWidth="1"/>
-    <col min="8" max="9" width="11.7272727272727" customWidth="1"/>
-    <col min="10" max="10" width="8.92727272727273" customWidth="1"/>
-    <col min="11" max="11" width="12.2636363636364" customWidth="1"/>
-    <col min="12" max="12" width="13.8636363636364" customWidth="1"/>
-    <col min="13" max="13" width="12.9272727272727" customWidth="1"/>
-    <col min="14" max="14" width="11.3363636363636" customWidth="1"/>
-    <col min="15" max="15" width="19.8636363636364" customWidth="1"/>
-    <col min="16" max="16" width="14.6636363636364" customWidth="1"/>
-    <col min="17" max="17" width="19.7272727272727" customWidth="1"/>
-    <col min="18" max="18" width="14.2636363636364" customWidth="1"/>
+    <col min="2" max="2" width="10.2666666666667" customWidth="1"/>
+    <col min="3" max="3" width="34.5238095238095" customWidth="1"/>
+    <col min="4" max="4" width="13.6" customWidth="1"/>
+    <col min="5" max="5" width="24.3619047619048" customWidth="1"/>
+    <col min="6" max="6" width="17.8666666666667" customWidth="1"/>
+    <col min="7" max="8" width="11.7238095238095" customWidth="1"/>
+    <col min="9" max="9" width="8.92380952380952" customWidth="1"/>
+    <col min="10" max="10" width="12.2666666666667" customWidth="1"/>
+    <col min="11" max="11" width="13.8666666666667" customWidth="1"/>
+    <col min="12" max="12" width="19.7238095238095" customWidth="1"/>
+    <col min="13" max="13" width="14.2666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="29" spans="1:12">
+    <row r="1" s="1" customFormat="1" ht="30" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -1365,10 +1359,10 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
@@ -1383,89 +1377,71 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+    </row>
+    <row r="2" ht="30" spans="1:13">
+      <c r="A2" s="4" t="s">
         <v>11</v>
       </c>
+      <c r="B2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4">
+        <v>8</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="5"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
     </row>
-    <row r="2" ht="29" spans="1:18">
-      <c r="A2" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="5">
-        <v>0</v>
-      </c>
-      <c r="F2" s="5">
-        <v>8</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="7"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-    </row>
-    <row r="3" ht="16" spans="1:18">
+    <row r="3" spans="1:13">
       <c r="A3" s="6"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
       <c r="H3" s="5"/>
       <c r="I3" s="7"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="9"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
     </row>
-    <row r="4" ht="16" spans="1:18">
+    <row r="4" spans="1:13">
       <c r="A4" s="6"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
       <c r="H4" s="5"/>
       <c r="I4" s="7"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="9"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Source/SmartInventory/SmartInventory/Content/Templates/Site/ImportSite.xlsx
+++ b/Source/SmartInventory/SmartInventory/Content/Templates/Site/ImportSite.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19035" windowHeight="7620"/>
+    <workbookView windowWidth="19635" windowHeight="7620"/>
   </bookViews>
   <sheets>
     <sheet name="Site" sheetId="1" r:id="rId1"/>
@@ -465,7 +465,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -486,28 +486,6 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -634,7 +612,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -646,34 +624,34 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -758,7 +736,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -780,10 +758,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -794,7 +769,7 @@
     <cellStyle name="Percent" xfId="3" builtinId="5"/>
     <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
     <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
     <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
@@ -1059,13 +1034,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1403,45 +1371,21 @@
         <v>15</v>
       </c>
       <c r="H2" s="5"/>
-      <c r="I2" s="7"/>
+      <c r="I2" s="5"/>
       <c r="J2" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:1">
       <c r="A3" s="6"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:1">
       <c r="A4" s="6"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
